--- a/canteen-react/public/report-template.xlsx
+++ b/canteen-react/public/report-template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B3EBDDE-41DD-451D-B914-DE825D4D9EC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05712A20-5696-46B7-AADA-02940AFB9269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1171,20 +1171,14 @@
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="H32" s="4"/>
-      <c r="I32" s="19">
-        <f>E42</f>
-        <v>0</v>
-      </c>
+      <c r="I32" s="19"/>
     </row>
     <row r="33" spans="1:10" ht="15.45" customHeight="1">
       <c r="A33" s="20"/>
       <c r="C33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
-      <c r="I33" s="18">
-        <f>SUM(I21:I32)</f>
-        <v>0</v>
-      </c>
+      <c r="I33" s="18"/>
     </row>
     <row r="34" spans="1:10" ht="15.45" customHeight="1">
       <c r="C34" s="2"/>

--- a/canteen-react/public/report-template.xlsx
+++ b/canteen-react/public/report-template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05712A20-5696-46B7-AADA-02940AFB9269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCAC3959-B2FF-4881-81E1-125C35A30567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -420,7 +420,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -490,6 +490,8 @@
     <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="7" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -854,60 +856,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.45" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
     </row>
     <row r="2" spans="1:12" ht="25.05" customHeight="1">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A3" s="51">
+      <c r="A3" s="53">
         <v>0</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
       <c r="J3" s="1"/>
     </row>
     <row r="4" spans="1:12" ht="15.45" customHeight="1">
-      <c r="A4" s="52">
+      <c r="A4" s="54">
         <v>0</v>
       </c>
-      <c r="B4" s="49"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="49"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
     </row>
     <row r="5" spans="1:12" ht="15.45" customHeight="1">
       <c r="C5" s="2"/>
@@ -1171,14 +1173,20 @@
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="H32" s="4"/>
-      <c r="I32" s="19"/>
+      <c r="I32" s="49">
+        <f>E42</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="33" spans="1:10" ht="15.45" customHeight="1">
       <c r="A33" s="20"/>
       <c r="C33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
-      <c r="I33" s="18"/>
+      <c r="I33" s="50">
+        <f>SUM(I21:I32)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="34" spans="1:10" ht="15.45" customHeight="1">
       <c r="C34" s="2"/>
@@ -1270,7 +1278,10 @@
         <v>34</v>
       </c>
       <c r="H42" s="4"/>
-      <c r="I42" s="9"/>
+      <c r="I42" s="9">
+        <f>SUM(I36:I41)</f>
+        <v>0</v>
+      </c>
       <c r="J42">
         <v>0</v>
       </c>
@@ -1402,60 +1413,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.45" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
     </row>
     <row r="2" spans="1:12" ht="25.05" customHeight="1">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="53" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
       <c r="J3" s="1"/>
     </row>
     <row r="4" spans="1:12" ht="15.45" customHeight="1">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="49"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="49"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
     </row>
     <row r="5" spans="1:12" ht="15.45" customHeight="1">
       <c r="C5" s="2"/>
@@ -1969,60 +1980,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.45" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
     </row>
     <row r="2" spans="1:12" ht="25.05" customHeight="1">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="53" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
       <c r="J3" s="1"/>
     </row>
     <row r="4" spans="1:12" ht="15.45" customHeight="1">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="B4" s="49"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="49"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
     </row>
     <row r="5" spans="1:12" ht="15.45" customHeight="1">
       <c r="C5" s="2"/>
@@ -2536,60 +2547,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.45" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
     </row>
     <row r="2" spans="1:12" ht="25.05" customHeight="1">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="53" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
       <c r="J3" s="1"/>
     </row>
     <row r="4" spans="1:12" ht="15.45" customHeight="1">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="49"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="49"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
     </row>
     <row r="5" spans="1:12" ht="15.45" customHeight="1">
       <c r="C5" s="2"/>
@@ -3102,60 +3113,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.45" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
     </row>
     <row r="2" spans="1:12" ht="25.05" customHeight="1">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="53" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
       <c r="J3" s="1"/>
     </row>
     <row r="4" spans="1:12" ht="15.45" customHeight="1">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="49"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="49"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
     </row>
     <row r="5" spans="1:12" ht="15.45" customHeight="1">
       <c r="C5" s="2"/>
@@ -3665,60 +3676,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.45" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
     </row>
     <row r="2" spans="1:12" ht="25.05" customHeight="1">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="53" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
       <c r="J3" s="1"/>
     </row>
     <row r="4" spans="1:12" ht="15.45" customHeight="1">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="54" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="49"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="49"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
     </row>
     <row r="5" spans="1:12" ht="15.45" customHeight="1">
       <c r="C5" s="2"/>
@@ -4230,60 +4241,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.45" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
     </row>
     <row r="2" spans="1:12" ht="25.05" customHeight="1">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="53" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
       <c r="J3" s="1"/>
     </row>
     <row r="4" spans="1:12" ht="15.45" customHeight="1">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="49"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="49"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
     </row>
     <row r="5" spans="1:12" ht="15.45" customHeight="1">
       <c r="C5" s="2"/>
@@ -4796,60 +4807,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.45" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
     </row>
     <row r="2" spans="1:12" ht="25.05" customHeight="1">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="53" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
       <c r="J3" s="1"/>
     </row>
     <row r="4" spans="1:12" ht="15.45" customHeight="1">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="49"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="49"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
     </row>
     <row r="5" spans="1:12" ht="15.45" customHeight="1">
       <c r="C5" s="2"/>
@@ -5357,60 +5368,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.45" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
     </row>
     <row r="2" spans="1:12" ht="25.05" customHeight="1">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="53" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
       <c r="J3" s="1"/>
     </row>
     <row r="4" spans="1:12" ht="15.45" customHeight="1">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="54" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="49"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="49"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
     </row>
     <row r="5" spans="1:12" ht="15.45" customHeight="1">
       <c r="C5" s="2"/>
@@ -5919,60 +5930,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.45" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
     </row>
     <row r="2" spans="1:12" ht="25.05" customHeight="1">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="53" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
       <c r="J3" s="1"/>
     </row>
     <row r="4" spans="1:12" ht="15.45" customHeight="1">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="B4" s="49"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="49"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
     </row>
     <row r="5" spans="1:12" ht="15.45" customHeight="1">
       <c r="C5" s="2"/>
@@ -6486,60 +6497,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.45" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
     </row>
     <row r="2" spans="1:12" ht="25.05" customHeight="1">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="53" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
       <c r="J3" s="1"/>
     </row>
     <row r="4" spans="1:12" ht="15.45" customHeight="1">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="B4" s="49"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="49"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
     </row>
     <row r="5" spans="1:12" ht="15.45" customHeight="1">
       <c r="C5" s="2"/>

--- a/canteen-react/public/report-template.xlsx
+++ b/canteen-react/public/report-template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCAC3959-B2FF-4881-81E1-125C35A30567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07A950FA-58E5-4567-B08D-6D8F1162C88E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1273,7 +1273,10 @@
       <c r="B42" s="28"/>
       <c r="C42" s="28"/>
       <c r="D42" s="27"/>
-      <c r="E42" s="29"/>
+      <c r="E42" s="29">
+        <f>SUM(E36:E41)</f>
+        <v>0</v>
+      </c>
       <c r="G42" s="10" t="s">
         <v>34</v>
       </c>

--- a/canteen-react/public/report-template.xlsx
+++ b/canteen-react/public/report-template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07A950FA-58E5-4567-B08D-6D8F1162C88E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE7BB2A5-3099-4CEE-91C9-EA77D782829D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1277,15 +1277,21 @@
         <f>SUM(E36:E41)</f>
         <v>0</v>
       </c>
-      <c r="G42" s="10" t="s">
+      <c r="G42" s="25">
+        <v>7</v>
+      </c>
+      <c r="H42" s="4"/>
+      <c r="I42" s="24"/>
+      <c r="J42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="13.95" customHeight="1" thickBot="1">
+      <c r="G43" t="s">
         <v>34</v>
       </c>
-      <c r="H42" s="4"/>
-      <c r="I42" s="9">
-        <f>SUM(I36:I41)</f>
-        <v>0</v>
-      </c>
-      <c r="J42">
+      <c r="I43" s="9">
+        <f>SUM(I36:I42)</f>
         <v>0</v>
       </c>
     </row>
